--- a/sources/table_normalization/xlsx/environment-table42.xlsx
+++ b/sources/table_normalization/xlsx/environment-table42.xlsx
@@ -240,7 +240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -258,7 +258,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -970,9 +969,9 @@
       <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="5">
         <f>AVERAGE(E2:E11)</f>
         <v>37.24</v>
@@ -987,9 +986,9 @@
       <c r="A13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="5">
         <f>STDEV(E2:E11)</f>
         <v>14.3767713884431</v>
@@ -1004,9 +1003,9 @@
       <c r="A14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="5">
         <f>E13/SQRT(10)</f>
         <v>4.54633429870215</v>
@@ -1227,9 +1226,9 @@
       <c r="A26" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="5">
         <f>AVERAGE(E16:E25)</f>
         <v>30.93</v>
@@ -1243,9 +1242,9 @@
       <c r="A27" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="5">
         <f>STDEV(E16:E25)</f>
         <v>5.0660196955356902</v>
@@ -1259,9 +1258,9 @@
       <c r="A28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
       <c r="E28" s="5">
         <f>E27/SQRT(10)</f>
         <v>1.60201609091655</v>
@@ -1601,9 +1600,9 @@
       <c r="A46" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
       <c r="E46" s="5">
         <f>AVERAGE(E30:E45)</f>
         <v>21.85</v>
@@ -1617,9 +1616,9 @@
       <c r="A47" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
       <c r="E47" s="5">
         <f>STDEV(E30:E45)</f>
         <v>8.2668817176329092</v>
@@ -1633,9 +1632,9 @@
       <c r="A48" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
       <c r="E48" s="5">
         <f>E47/SQRT(16)</f>
         <v>2.06672042940823</v>
@@ -1935,9 +1934,9 @@
       <c r="A64" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
       <c r="E64" s="5">
         <f>AVERAGE(E50:E63)</f>
         <v>17.907142857142901</v>
@@ -1951,9 +1950,9 @@
       <c r="A65" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
       <c r="E65" s="5">
         <f>STDEV(E50:E63)</f>
         <v>10.457346647266601</v>
@@ -1967,9 +1966,9 @@
       <c r="A66" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
       <c r="E66" s="5">
         <f>E65/SQRT(14)</f>
         <v>2.7948434520572101</v>
@@ -2149,9 +2148,9 @@
       <c r="A76" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
       <c r="E76" s="5">
         <f>AVERAGE(E68:E75)</f>
         <v>14.324999999999999</v>
@@ -2165,9 +2164,9 @@
       <c r="A77" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
       <c r="E77" s="5">
         <f>STDEV(E68:E75)</f>
         <v>6.4670041639960996</v>
@@ -2181,9 +2180,9 @@
       <c r="A78" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
       <c r="E78" s="5">
         <f>E77/SQRT(8)</f>
         <v>2.2864312491616401</v>
@@ -2383,9 +2382,6 @@
       <c r="A89" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B89" s="7"/>
-      <c r="C89" s="7"/>
-      <c r="D89" s="7"/>
       <c r="E89" s="5">
         <f>AVERAGE(E80:E88)</f>
         <v>15.977777777777799</v>
@@ -2399,9 +2395,6 @@
       <c r="A90" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B90" s="7"/>
-      <c r="C90" s="7"/>
-      <c r="D90" s="7"/>
       <c r="E90" s="5">
         <f>STDEV(E80:E88)</f>
         <v>6.9035820009937199</v>
@@ -2415,9 +2408,6 @@
       <c r="A91" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
       <c r="E91" s="5">
         <f>E90/SQRT(9)</f>
         <v>2.3011940003312401</v>
